--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124510904</v>
+        <v>124511273</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458110</v>
+        <v>458076</v>
       </c>
       <c r="R2" t="n">
-        <v>6944193</v>
+        <v>6944155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,17 +777,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511633</v>
+        <v>124511723</v>
       </c>
       <c r="B3" t="n">
         <v>91299</v>
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458165</v>
+        <v>458198</v>
       </c>
       <c r="R3" t="n">
-        <v>6944152</v>
+        <v>6944084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511683</v>
+        <v>124511262</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -978,14 +978,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458193</v>
+        <v>458076</v>
       </c>
       <c r="R4" t="n">
-        <v>6944142</v>
+        <v>6944155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511528</v>
+        <v>124511616</v>
       </c>
       <c r="B5" t="n">
         <v>91012</v>
@@ -1108,14 +1108,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458148</v>
+        <v>458165</v>
       </c>
       <c r="R5" t="n">
-        <v>6944110</v>
+        <v>6944152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,6 +1150,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1167,17 +1172,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1321,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511018</v>
+        <v>124511683</v>
       </c>
       <c r="B7" t="n">
-        <v>91592</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1333,25 +1338,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1179</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1364,14 +1369,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458095</v>
+        <v>458193</v>
       </c>
       <c r="R7" t="n">
-        <v>6944168</v>
+        <v>6944142</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1431,14 +1436,9 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124511471</v>
+        <v>124511018</v>
       </c>
       <c r="B8" t="n">
         <v>91592</v>
@@ -1499,14 +1499,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458133</v>
+        <v>458095</v>
       </c>
       <c r="R8" t="n">
-        <v>6944117</v>
+        <v>6944168</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1558,17 +1558,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1586,10 +1591,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511273</v>
+        <v>124510922</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1602,21 +1607,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1629,14 +1634,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458076</v>
+        <v>458110</v>
       </c>
       <c r="R9" t="n">
-        <v>6944155</v>
+        <v>6944193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1688,17 +1693,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1716,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511080</v>
+        <v>124511576</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1732,21 +1737,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1759,14 +1764,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458100</v>
+        <v>458165</v>
       </c>
       <c r="R10" t="n">
-        <v>6944149</v>
+        <v>6944152</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1801,6 +1806,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>En låga med flertal kroppar på</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1818,17 +1828,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1846,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511616</v>
+        <v>124511471</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1858,25 +1868,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1889,14 +1899,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458165</v>
+        <v>458133</v>
       </c>
       <c r="R11" t="n">
-        <v>6944152</v>
+        <v>6944117</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1931,11 +1941,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1953,17 +1958,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1981,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124510922</v>
+        <v>124511080</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1997,21 +2002,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2024,14 +2029,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458110</v>
+        <v>458100</v>
       </c>
       <c r="R12" t="n">
-        <v>6944193</v>
+        <v>6944149</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2083,17 +2088,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2111,10 +2116,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511262</v>
+        <v>124511528</v>
       </c>
       <c r="B13" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2123,25 +2128,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2154,14 +2159,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458076</v>
+        <v>458148</v>
       </c>
       <c r="R13" t="n">
-        <v>6944155</v>
+        <v>6944110</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2213,17 +2218,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2241,7 +2246,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511723</v>
+        <v>124510904</v>
       </c>
       <c r="B14" t="n">
         <v>91299</v>
@@ -2284,14 +2289,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458198</v>
+        <v>458110</v>
       </c>
       <c r="R14" t="n">
-        <v>6944084</v>
+        <v>6944193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2343,17 +2348,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511273</v>
+        <v>124510904</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458076</v>
+        <v>458110</v>
       </c>
       <c r="R2" t="n">
-        <v>6944155</v>
+        <v>6944193</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,17 +777,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511723</v>
+        <v>124511018</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>91592</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458198</v>
+        <v>458095</v>
       </c>
       <c r="R3" t="n">
-        <v>6944084</v>
+        <v>6944168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -915,9 +915,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1065,7 +1070,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511616</v>
+        <v>124511528</v>
       </c>
       <c r="B5" t="n">
         <v>91012</v>
@@ -1108,14 +1113,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458165</v>
+        <v>458148</v>
       </c>
       <c r="R5" t="n">
-        <v>6944152</v>
+        <v>6944110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,11 +1155,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1172,17 +1172,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511124</v>
+        <v>124511727</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,37 +1216,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458128</v>
+        <v>458198</v>
       </c>
       <c r="R6" t="n">
-        <v>6944149</v>
+        <v>6944084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1326,7 +1330,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511683</v>
+        <v>124511633</v>
       </c>
       <c r="B7" t="n">
         <v>91299</v>
@@ -1369,14 +1373,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458193</v>
+        <v>458165</v>
       </c>
       <c r="R7" t="n">
-        <v>6944142</v>
+        <v>6944152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1456,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124511018</v>
+        <v>124511124</v>
       </c>
       <c r="B8" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1468,45 +1472,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458095</v>
+        <v>458128</v>
       </c>
       <c r="R8" t="n">
-        <v>6944168</v>
+        <v>6944149</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1566,14 +1566,9 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1591,10 +1586,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124510922</v>
+        <v>124511616</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1607,21 +1602,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1634,14 +1629,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458110</v>
+        <v>458165</v>
       </c>
       <c r="R9" t="n">
-        <v>6944193</v>
+        <v>6944152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1676,6 +1671,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1693,17 +1693,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511576</v>
+        <v>124511471</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>91592</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1733,25 +1733,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1179</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1764,14 +1764,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458165</v>
+        <v>458133</v>
       </c>
       <c r="R10" t="n">
-        <v>6944152</v>
+        <v>6944117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,11 +1804,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>En låga med flertal kroppar på</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1856,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511471</v>
+        <v>124511273</v>
       </c>
       <c r="B11" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1868,25 +1863,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1899,14 +1894,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458133</v>
+        <v>458076</v>
       </c>
       <c r="R11" t="n">
-        <v>6944117</v>
+        <v>6944155</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1958,17 +1953,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2116,10 +2111,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511528</v>
+        <v>124511683</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2132,21 +2127,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2159,14 +2154,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458148</v>
+        <v>458193</v>
       </c>
       <c r="R13" t="n">
-        <v>6944110</v>
+        <v>6944142</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2218,17 +2213,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2246,10 +2241,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124510904</v>
+        <v>124510922</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2262,21 +2257,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124510904</v>
+        <v>124510922</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511018</v>
+        <v>124511471</v>
       </c>
       <c r="B3" t="n">
         <v>91592</v>
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458095</v>
+        <v>458133</v>
       </c>
       <c r="R3" t="n">
-        <v>6944168</v>
+        <v>6944117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,22 +907,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511262</v>
+        <v>124511723</v>
       </c>
       <c r="B4" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -983,14 +978,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458076</v>
+        <v>458198</v>
       </c>
       <c r="R4" t="n">
-        <v>6944155</v>
+        <v>6944084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1070,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511528</v>
+        <v>124511683</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1113,14 +1108,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458148</v>
+        <v>458193</v>
       </c>
       <c r="R5" t="n">
-        <v>6944110</v>
+        <v>6944142</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1172,17 +1167,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511727</v>
+        <v>124511616</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,14 +1238,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458198</v>
+        <v>458165</v>
       </c>
       <c r="R6" t="n">
-        <v>6944084</v>
+        <v>6944152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1283,6 +1278,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511633</v>
+        <v>124511262</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1373,14 +1373,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458165</v>
+        <v>458076</v>
       </c>
       <c r="R7" t="n">
-        <v>6944152</v>
+        <v>6944155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124511124</v>
+        <v>124510904</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,37 +1476,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458128</v>
+        <v>458110</v>
       </c>
       <c r="R8" t="n">
-        <v>6944149</v>
+        <v>6944193</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1558,17 +1562,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1586,7 +1590,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511616</v>
+        <v>124511528</v>
       </c>
       <c r="B9" t="n">
         <v>91012</v>
@@ -1629,14 +1633,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458165</v>
+        <v>458148</v>
       </c>
       <c r="R9" t="n">
-        <v>6944152</v>
+        <v>6944110</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1671,11 +1675,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1693,17 +1692,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1721,7 +1720,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511471</v>
+        <v>124511018</v>
       </c>
       <c r="B10" t="n">
         <v>91592</v>
@@ -1764,14 +1763,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458133</v>
+        <v>458095</v>
       </c>
       <c r="R10" t="n">
-        <v>6944117</v>
+        <v>6944168</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1823,17 +1822,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1851,7 +1855,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511273</v>
+        <v>124511124</v>
       </c>
       <c r="B11" t="n">
         <v>91012</v>
@@ -1885,23 +1889,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458076</v>
+        <v>458128</v>
       </c>
       <c r="R11" t="n">
-        <v>6944155</v>
+        <v>6944149</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2111,10 +2111,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511683</v>
+        <v>124511273</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2127,21 +2127,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2154,14 +2154,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458193</v>
+        <v>458076</v>
       </c>
       <c r="R13" t="n">
-        <v>6944142</v>
+        <v>6944155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124510922</v>
+        <v>124511633</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2284,14 +2284,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458110</v>
+        <v>458165</v>
       </c>
       <c r="R14" t="n">
-        <v>6944193</v>
+        <v>6944152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2343,17 +2343,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124510922</v>
+        <v>124511723</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458110</v>
+        <v>458198</v>
       </c>
       <c r="R2" t="n">
-        <v>6944193</v>
+        <v>6944084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,17 +777,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511471</v>
+        <v>124511124</v>
       </c>
       <c r="B3" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,45 +817,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458133</v>
+        <v>458128</v>
       </c>
       <c r="R3" t="n">
-        <v>6944117</v>
+        <v>6944149</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,17 +903,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511723</v>
+        <v>124511528</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +947,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -978,14 +974,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458198</v>
+        <v>458148</v>
       </c>
       <c r="R4" t="n">
-        <v>6944084</v>
+        <v>6944110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1037,17 +1033,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1065,7 +1061,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511683</v>
+        <v>124511576</v>
       </c>
       <c r="B5" t="n">
         <v>91299</v>
@@ -1108,14 +1104,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458193</v>
+        <v>458165</v>
       </c>
       <c r="R5" t="n">
-        <v>6944142</v>
+        <v>6944152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,6 +1146,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En låga med flertal kroppar på</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1167,17 +1168,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511616</v>
+        <v>124510922</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,21 +1212,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1238,14 +1239,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458165</v>
+        <v>458110</v>
       </c>
       <c r="R6" t="n">
-        <v>6944152</v>
+        <v>6944193</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,11 +1281,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1302,17 +1298,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1330,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511262</v>
+        <v>124511273</v>
       </c>
       <c r="B7" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1338,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1590,10 +1586,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511528</v>
+        <v>124511683</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1606,21 +1602,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1633,14 +1629,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458148</v>
+        <v>458193</v>
       </c>
       <c r="R9" t="n">
-        <v>6944110</v>
+        <v>6944142</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1692,17 +1688,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1720,10 +1716,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511018</v>
+        <v>124511262</v>
       </c>
       <c r="B10" t="n">
-        <v>91592</v>
+        <v>91457</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,21 +1732,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1179</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1763,14 +1759,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458095</v>
+        <v>458076</v>
       </c>
       <c r="R10" t="n">
-        <v>6944168</v>
+        <v>6944155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1830,14 +1826,9 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1855,7 +1846,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511124</v>
+        <v>124511616</v>
       </c>
       <c r="B11" t="n">
         <v>91012</v>
@@ -1889,19 +1880,23 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458128</v>
+        <v>458165</v>
       </c>
       <c r="R11" t="n">
-        <v>6944149</v>
+        <v>6944152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1934,6 +1929,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1981,10 +1981,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124511080</v>
+        <v>124511471</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1993,25 +1993,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2024,14 +2024,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458100</v>
+        <v>458133</v>
       </c>
       <c r="R12" t="n">
-        <v>6944149</v>
+        <v>6944117</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2083,17 +2083,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511273</v>
+        <v>124511018</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2123,25 +2123,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2154,14 +2154,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458076</v>
+        <v>458095</v>
       </c>
       <c r="R13" t="n">
-        <v>6944155</v>
+        <v>6944168</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2221,9 +2221,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2241,10 +2246,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511633</v>
+        <v>124511080</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2257,21 +2262,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2284,14 +2289,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458165</v>
+        <v>458100</v>
       </c>
       <c r="R14" t="n">
-        <v>6944152</v>
+        <v>6944149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511723</v>
+        <v>124511018</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>91592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458198</v>
+        <v>458095</v>
       </c>
       <c r="R2" t="n">
-        <v>6944084</v>
+        <v>6944168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,9 +785,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511124</v>
+        <v>124511080</v>
       </c>
       <c r="B3" t="n">
         <v>91012</v>
@@ -839,16 +844,20 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458128</v>
+        <v>458100</v>
       </c>
       <c r="R3" t="n">
         <v>6944149</v>
@@ -931,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511528</v>
+        <v>124511723</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,21 +956,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,14 +983,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458148</v>
+        <v>458198</v>
       </c>
       <c r="R4" t="n">
-        <v>6944110</v>
+        <v>6944084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1033,17 +1042,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511576</v>
+        <v>124510922</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1104,14 +1113,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458165</v>
+        <v>458110</v>
       </c>
       <c r="R5" t="n">
-        <v>6944152</v>
+        <v>6944193</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,11 +1153,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>En låga med flertal kroppar på</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1196,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124510922</v>
+        <v>124511616</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,21 +1216,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,14 +1243,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458110</v>
+        <v>458165</v>
       </c>
       <c r="R6" t="n">
-        <v>6944193</v>
+        <v>6944152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1281,6 +1285,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1298,17 +1307,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1586,7 +1595,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511683</v>
+        <v>124511576</v>
       </c>
       <c r="B9" t="n">
         <v>91299</v>
@@ -1629,14 +1638,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458193</v>
+        <v>458165</v>
       </c>
       <c r="R9" t="n">
-        <v>6944142</v>
+        <v>6944152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1671,6 +1680,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En låga med flertal kroppar på</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1688,17 +1702,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1716,10 +1730,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511262</v>
+        <v>124511124</v>
       </c>
       <c r="B10" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1728,45 +1742,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458076</v>
+        <v>458128</v>
       </c>
       <c r="R10" t="n">
-        <v>6944155</v>
+        <v>6944149</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1846,7 +1856,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511616</v>
+        <v>124511528</v>
       </c>
       <c r="B11" t="n">
         <v>91012</v>
@@ -1889,14 +1899,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458165</v>
+        <v>458148</v>
       </c>
       <c r="R11" t="n">
-        <v>6944152</v>
+        <v>6944110</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1931,11 +1941,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1953,17 +1958,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1981,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124511471</v>
+        <v>124511683</v>
       </c>
       <c r="B12" t="n">
-        <v>91592</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1993,25 +1998,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1179</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2024,14 +2029,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458133</v>
+        <v>458193</v>
       </c>
       <c r="R12" t="n">
-        <v>6944117</v>
+        <v>6944142</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2083,17 +2088,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2111,7 +2116,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511018</v>
+        <v>124511471</v>
       </c>
       <c r="B13" t="n">
         <v>91592</v>
@@ -2154,14 +2159,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458095</v>
+        <v>458133</v>
       </c>
       <c r="R13" t="n">
-        <v>6944168</v>
+        <v>6944117</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2213,22 +2218,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511080</v>
+        <v>124511262</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2258,25 +2258,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2289,14 +2289,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458100</v>
+        <v>458076</v>
       </c>
       <c r="R14" t="n">
-        <v>6944149</v>
+        <v>6944155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511018</v>
+        <v>124511262</v>
       </c>
       <c r="B2" t="n">
-        <v>91592</v>
+        <v>91457</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1179</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458095</v>
+        <v>458076</v>
       </c>
       <c r="R2" t="n">
-        <v>6944168</v>
+        <v>6944155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,14 +785,9 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511080</v>
+        <v>124510904</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -853,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458100</v>
+        <v>458110</v>
       </c>
       <c r="R3" t="n">
-        <v>6944149</v>
+        <v>6944193</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,17 +907,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,7 +935,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511723</v>
+        <v>124511576</v>
       </c>
       <c r="B4" t="n">
         <v>91299</v>
@@ -983,14 +978,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458198</v>
+        <v>458165</v>
       </c>
       <c r="R4" t="n">
-        <v>6944084</v>
+        <v>6944152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,6 +1020,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En låga med flertal kroppar på</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1042,17 +1042,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124510922</v>
+        <v>124511723</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1113,14 +1113,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458110</v>
+        <v>458198</v>
       </c>
       <c r="R5" t="n">
-        <v>6944193</v>
+        <v>6944084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1172,17 +1172,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511616</v>
+        <v>124511471</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,14 +1243,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458165</v>
+        <v>458133</v>
       </c>
       <c r="R6" t="n">
-        <v>6944152</v>
+        <v>6944117</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,11 +1285,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1307,17 +1302,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511273</v>
+        <v>124511683</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1378,14 +1373,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458076</v>
+        <v>458193</v>
       </c>
       <c r="R7" t="n">
-        <v>6944155</v>
+        <v>6944142</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1465,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124510904</v>
+        <v>124511528</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1481,21 +1476,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1508,14 +1503,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458110</v>
+        <v>458148</v>
       </c>
       <c r="R8" t="n">
-        <v>6944193</v>
+        <v>6944110</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1595,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511576</v>
+        <v>124510922</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,21 +1606,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1638,14 +1633,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458165</v>
+        <v>458110</v>
       </c>
       <c r="R9" t="n">
-        <v>6944152</v>
+        <v>6944193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,11 +1673,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En låga med flertal kroppar på</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1730,7 +1720,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511124</v>
+        <v>124511616</v>
       </c>
       <c r="B10" t="n">
         <v>91012</v>
@@ -1764,19 +1754,23 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458128</v>
+        <v>458165</v>
       </c>
       <c r="R10" t="n">
-        <v>6944149</v>
+        <v>6944152</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,6 +1803,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1856,7 +1855,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511528</v>
+        <v>124511273</v>
       </c>
       <c r="B11" t="n">
         <v>91012</v>
@@ -1899,14 +1898,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458148</v>
+        <v>458076</v>
       </c>
       <c r="R11" t="n">
-        <v>6944110</v>
+        <v>6944155</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1958,17 +1957,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1986,10 +1985,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124511683</v>
+        <v>124511080</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2002,21 +2001,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2029,14 +2028,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458193</v>
+        <v>458100</v>
       </c>
       <c r="R12" t="n">
-        <v>6944142</v>
+        <v>6944149</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2116,10 +2115,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511471</v>
+        <v>124511124</v>
       </c>
       <c r="B13" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2128,45 +2127,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458133</v>
+        <v>458128</v>
       </c>
       <c r="R13" t="n">
-        <v>6944117</v>
+        <v>6944149</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2218,17 +2213,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2246,10 +2241,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511262</v>
+        <v>124511018</v>
       </c>
       <c r="B14" t="n">
-        <v>91457</v>
+        <v>91592</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2262,21 +2257,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1179</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2289,14 +2284,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458076</v>
+        <v>458095</v>
       </c>
       <c r="R14" t="n">
-        <v>6944155</v>
+        <v>6944168</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2356,9 +2351,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511262</v>
+        <v>124511124</v>
       </c>
       <c r="B2" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458076</v>
+        <v>458128</v>
       </c>
       <c r="R2" t="n">
-        <v>6944155</v>
+        <v>6944149</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -805,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124510904</v>
+        <v>124511683</v>
       </c>
       <c r="B3" t="n">
         <v>91299</v>
@@ -848,14 +844,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458110</v>
+        <v>458193</v>
       </c>
       <c r="R3" t="n">
-        <v>6944193</v>
+        <v>6944142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,17 +903,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,7 +931,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511576</v>
+        <v>124510904</v>
       </c>
       <c r="B4" t="n">
         <v>91299</v>
@@ -978,14 +974,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458165</v>
+        <v>458110</v>
       </c>
       <c r="R4" t="n">
-        <v>6944152</v>
+        <v>6944193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,11 +1014,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En låga med flertal kroppar på</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511723</v>
+        <v>124511262</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,25 +1073,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1113,14 +1104,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458198</v>
+        <v>458076</v>
       </c>
       <c r="R5" t="n">
-        <v>6944084</v>
+        <v>6944155</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1330,10 +1321,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511683</v>
+        <v>124510922</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1337,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1373,14 +1364,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458193</v>
+        <v>458110</v>
       </c>
       <c r="R7" t="n">
-        <v>6944142</v>
+        <v>6944193</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1432,17 +1423,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1460,7 +1451,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124511528</v>
+        <v>124511273</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1503,14 +1494,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458148</v>
+        <v>458076</v>
       </c>
       <c r="R8" t="n">
-        <v>6944110</v>
+        <v>6944155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1562,17 +1553,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1590,10 +1581,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124510922</v>
+        <v>124511616</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1606,21 +1597,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1633,14 +1624,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458110</v>
+        <v>458165</v>
       </c>
       <c r="R9" t="n">
-        <v>6944193</v>
+        <v>6944152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,6 +1666,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1692,17 +1688,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1720,10 +1716,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511616</v>
+        <v>124511576</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,21 +1732,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1807,7 +1803,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>En låga med ullticka på</t>
+          <t>En låga med flertal kroppar på</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1827,17 +1823,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1855,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511273</v>
+        <v>124511018</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1867,25 +1863,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1898,14 +1894,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458076</v>
+        <v>458095</v>
       </c>
       <c r="R11" t="n">
-        <v>6944155</v>
+        <v>6944168</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1965,9 +1961,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1985,7 +1986,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124511080</v>
+        <v>124511528</v>
       </c>
       <c r="B12" t="n">
         <v>91012</v>
@@ -2028,14 +2029,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458100</v>
+        <v>458148</v>
       </c>
       <c r="R12" t="n">
-        <v>6944149</v>
+        <v>6944110</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2087,17 +2088,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2115,7 +2116,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511124</v>
+        <v>124511080</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -2149,16 +2150,20 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458128</v>
+        <v>458100</v>
       </c>
       <c r="R13" t="n">
         <v>6944149</v>
@@ -2241,10 +2246,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511018</v>
+        <v>124511723</v>
       </c>
       <c r="B14" t="n">
-        <v>91592</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2253,25 +2258,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1179</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2284,14 +2289,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458095</v>
+        <v>458198</v>
       </c>
       <c r="R14" t="n">
-        <v>6944168</v>
+        <v>6944084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2351,14 +2356,9 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511124</v>
+        <v>124511471</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458128</v>
+        <v>458133</v>
       </c>
       <c r="R2" t="n">
-        <v>6944149</v>
+        <v>6944117</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -773,17 +777,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511683</v>
+        <v>124511018</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>91592</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458193</v>
+        <v>458095</v>
       </c>
       <c r="R3" t="n">
-        <v>6944142</v>
+        <v>6944168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,9 +915,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -931,7 +940,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124510904</v>
+        <v>124511683</v>
       </c>
       <c r="B4" t="n">
         <v>91299</v>
@@ -974,14 +983,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458110</v>
+        <v>458193</v>
       </c>
       <c r="R4" t="n">
-        <v>6944193</v>
+        <v>6944142</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1033,17 +1042,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511262</v>
+        <v>124511080</v>
       </c>
       <c r="B5" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,25 +1082,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1104,14 +1113,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458076</v>
+        <v>458100</v>
       </c>
       <c r="R5" t="n">
-        <v>6944155</v>
+        <v>6944149</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1191,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511471</v>
+        <v>124511633</v>
       </c>
       <c r="B6" t="n">
-        <v>91592</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,25 +1212,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1179</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1234,14 +1243,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458133</v>
+        <v>458165</v>
       </c>
       <c r="R6" t="n">
-        <v>6944117</v>
+        <v>6944152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1293,17 +1302,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1321,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124510922</v>
+        <v>124511262</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1333,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1364,14 +1373,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458110</v>
+        <v>458076</v>
       </c>
       <c r="R7" t="n">
-        <v>6944193</v>
+        <v>6944155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1423,17 +1432,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1451,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124511273</v>
+        <v>124510922</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,21 +1476,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1494,14 +1503,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458076</v>
+        <v>458110</v>
       </c>
       <c r="R8" t="n">
-        <v>6944155</v>
+        <v>6944193</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1553,17 +1562,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1581,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511616</v>
+        <v>124510904</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,21 +1606,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1624,14 +1633,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458165</v>
+        <v>458110</v>
       </c>
       <c r="R9" t="n">
-        <v>6944152</v>
+        <v>6944193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1666,11 +1675,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1688,17 +1692,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1716,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511576</v>
+        <v>124511528</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1732,21 +1736,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1759,14 +1763,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458165</v>
+        <v>458148</v>
       </c>
       <c r="R10" t="n">
-        <v>6944152</v>
+        <v>6944110</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,11 +1803,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>En låga med flertal kroppar på</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1851,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511018</v>
+        <v>124511723</v>
       </c>
       <c r="B11" t="n">
-        <v>91592</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1863,25 +1862,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1179</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1894,14 +1893,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458095</v>
+        <v>458198</v>
       </c>
       <c r="R11" t="n">
-        <v>6944168</v>
+        <v>6944084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1961,14 +1960,9 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1986,7 +1980,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124511528</v>
+        <v>124511616</v>
       </c>
       <c r="B12" t="n">
         <v>91012</v>
@@ -2029,14 +2023,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458148</v>
+        <v>458165</v>
       </c>
       <c r="R12" t="n">
-        <v>6944110</v>
+        <v>6944152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,6 +2065,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2088,17 +2087,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2116,7 +2115,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511080</v>
+        <v>124511273</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -2159,14 +2158,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458100</v>
+        <v>458076</v>
       </c>
       <c r="R13" t="n">
-        <v>6944149</v>
+        <v>6944155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2246,10 +2245,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511723</v>
+        <v>124511124</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2262,41 +2261,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458198</v>
+        <v>458128</v>
       </c>
       <c r="R14" t="n">
-        <v>6944084</v>
+        <v>6944149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511471</v>
+        <v>124511124</v>
       </c>
       <c r="B2" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458133</v>
+        <v>458128</v>
       </c>
       <c r="R2" t="n">
-        <v>6944117</v>
+        <v>6944149</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,17 +773,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511018</v>
+        <v>124510904</v>
       </c>
       <c r="B3" t="n">
-        <v>91592</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1179</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -848,14 +844,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458095</v>
+        <v>458110</v>
       </c>
       <c r="R3" t="n">
-        <v>6944168</v>
+        <v>6944193</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,22 +903,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1070,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511080</v>
+        <v>124511576</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1077,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1113,14 +1104,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458100</v>
+        <v>458165</v>
       </c>
       <c r="R5" t="n">
-        <v>6944149</v>
+        <v>6944152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1155,6 +1146,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En låga med flertal kroppar på</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1172,17 +1168,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1200,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511633</v>
+        <v>124511471</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91592</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,25 +1208,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1179</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,14 +1239,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458165</v>
+        <v>458133</v>
       </c>
       <c r="R6" t="n">
-        <v>6944152</v>
+        <v>6944117</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1302,17 +1298,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1330,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511262</v>
+        <v>124511018</v>
       </c>
       <c r="B7" t="n">
-        <v>91457</v>
+        <v>91592</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1342,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1179</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1373,14 +1369,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458076</v>
+        <v>458095</v>
       </c>
       <c r="R7" t="n">
-        <v>6944155</v>
+        <v>6944168</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1440,9 +1436,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1460,10 +1461,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124510922</v>
+        <v>124511528</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,21 +1477,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1503,14 +1504,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458110</v>
+        <v>458148</v>
       </c>
       <c r="R8" t="n">
-        <v>6944193</v>
+        <v>6944110</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1590,7 +1591,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124510904</v>
+        <v>124511727</v>
       </c>
       <c r="B9" t="n">
         <v>91299</v>
@@ -1633,14 +1634,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458110</v>
+        <v>458198</v>
       </c>
       <c r="R9" t="n">
-        <v>6944193</v>
+        <v>6944084</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1692,17 +1693,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1720,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511528</v>
+        <v>124510922</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,21 +1737,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1763,14 +1764,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458148</v>
+        <v>458110</v>
       </c>
       <c r="R10" t="n">
-        <v>6944110</v>
+        <v>6944193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1850,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511723</v>
+        <v>124511080</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1866,21 +1867,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1893,14 +1894,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458198</v>
+        <v>458100</v>
       </c>
       <c r="R11" t="n">
-        <v>6944084</v>
+        <v>6944149</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1980,10 +1981,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124511616</v>
+        <v>124511262</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1992,25 +1993,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2023,14 +2024,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458165</v>
+        <v>458076</v>
       </c>
       <c r="R12" t="n">
-        <v>6944152</v>
+        <v>6944155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2063,11 +2064,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2115,7 +2111,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511273</v>
+        <v>124511616</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -2158,14 +2154,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458076</v>
+        <v>458165</v>
       </c>
       <c r="R13" t="n">
-        <v>6944155</v>
+        <v>6944152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2198,6 +2194,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2245,7 +2246,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511124</v>
+        <v>124511273</v>
       </c>
       <c r="B14" t="n">
         <v>91012</v>
@@ -2279,19 +2280,23 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458128</v>
+        <v>458076</v>
       </c>
       <c r="R14" t="n">
-        <v>6944149</v>
+        <v>6944155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511124</v>
+        <v>124511262</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458128</v>
+        <v>458076</v>
       </c>
       <c r="R2" t="n">
-        <v>6944149</v>
+        <v>6944155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -801,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124510904</v>
+        <v>124511471</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>91592</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458110</v>
+        <v>458133</v>
       </c>
       <c r="R3" t="n">
-        <v>6944193</v>
+        <v>6944117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -931,7 +935,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511683</v>
+        <v>124511727</v>
       </c>
       <c r="B4" t="n">
         <v>91299</v>
@@ -974,14 +978,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458193</v>
+        <v>458198</v>
       </c>
       <c r="R4" t="n">
-        <v>6944142</v>
+        <v>6944084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1061,7 +1065,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511576</v>
+        <v>124511683</v>
       </c>
       <c r="B5" t="n">
         <v>91299</v>
@@ -1104,14 +1108,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458165</v>
+        <v>458193</v>
       </c>
       <c r="R5" t="n">
-        <v>6944152</v>
+        <v>6944142</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,11 +1150,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>En låga med flertal kroppar på</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1168,17 +1167,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1196,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511471</v>
+        <v>124511576</v>
       </c>
       <c r="B6" t="n">
-        <v>91592</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,25 +1207,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1179</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,14 +1238,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458133</v>
+        <v>458165</v>
       </c>
       <c r="R6" t="n">
-        <v>6944117</v>
+        <v>6944152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,6 +1278,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En låga med flertal kroppar på</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511018</v>
+        <v>124511616</v>
       </c>
       <c r="B7" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1369,14 +1373,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458095</v>
+        <v>458165</v>
       </c>
       <c r="R7" t="n">
-        <v>6944168</v>
+        <v>6944152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,6 +1415,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1436,14 +1445,9 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1461,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124511528</v>
+        <v>124511018</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1473,25 +1477,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1504,14 +1508,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458148</v>
+        <v>458095</v>
       </c>
       <c r="R8" t="n">
-        <v>6944110</v>
+        <v>6944168</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1563,17 +1567,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1591,10 +1600,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511727</v>
+        <v>124511273</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1607,21 +1616,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1634,14 +1643,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458198</v>
+        <v>458076</v>
       </c>
       <c r="R9" t="n">
-        <v>6944084</v>
+        <v>6944155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1721,10 +1730,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124510922</v>
+        <v>124511080</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1737,21 +1746,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1764,14 +1773,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458110</v>
+        <v>458100</v>
       </c>
       <c r="R10" t="n">
-        <v>6944193</v>
+        <v>6944149</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1823,17 +1832,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1851,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511080</v>
+        <v>124510904</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1867,21 +1876,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1894,14 +1903,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458100</v>
+        <v>458110</v>
       </c>
       <c r="R11" t="n">
-        <v>6944149</v>
+        <v>6944193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1953,17 +1962,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1981,10 +1990,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124511262</v>
+        <v>124510922</v>
       </c>
       <c r="B12" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1993,25 +2002,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2024,14 +2033,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458076</v>
+        <v>458110</v>
       </c>
       <c r="R12" t="n">
-        <v>6944155</v>
+        <v>6944193</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2083,17 +2092,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2111,7 +2120,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511616</v>
+        <v>124511528</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -2154,14 +2163,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458165</v>
+        <v>458148</v>
       </c>
       <c r="R13" t="n">
-        <v>6944152</v>
+        <v>6944110</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2196,11 +2205,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2218,17 +2222,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2246,7 +2250,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511273</v>
+        <v>124511124</v>
       </c>
       <c r="B14" t="n">
         <v>91012</v>
@@ -2280,23 +2284,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458076</v>
+        <v>458128</v>
       </c>
       <c r="R14" t="n">
-        <v>6944155</v>
+        <v>6944149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511262</v>
+        <v>124511528</v>
       </c>
       <c r="B2" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458076</v>
+        <v>458148</v>
       </c>
       <c r="R2" t="n">
-        <v>6944155</v>
+        <v>6944110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,17 +777,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511727</v>
+        <v>124511262</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -978,14 +978,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458198</v>
+        <v>458076</v>
       </c>
       <c r="R4" t="n">
-        <v>6944084</v>
+        <v>6944155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511683</v>
+        <v>124510922</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1108,14 +1108,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458193</v>
+        <v>458110</v>
       </c>
       <c r="R5" t="n">
-        <v>6944142</v>
+        <v>6944193</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511576</v>
+        <v>124511124</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,41 +1211,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458165</v>
+        <v>458128</v>
       </c>
       <c r="R6" t="n">
-        <v>6944152</v>
+        <v>6944149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,11 +1276,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En låga med flertal kroppar på</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1302,17 +1293,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1330,10 +1321,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511616</v>
+        <v>124511683</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1337,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1373,14 +1364,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458165</v>
+        <v>458193</v>
       </c>
       <c r="R7" t="n">
-        <v>6944152</v>
+        <v>6944142</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,11 +1404,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1465,10 +1451,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124511018</v>
+        <v>124511616</v>
       </c>
       <c r="B8" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1477,25 +1463,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1508,14 +1494,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458095</v>
+        <v>458165</v>
       </c>
       <c r="R8" t="n">
-        <v>6944168</v>
+        <v>6944152</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1550,6 +1536,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1575,14 +1566,9 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1600,10 +1586,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511273</v>
+        <v>124511633</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1616,21 +1602,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1643,14 +1629,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458076</v>
+        <v>458165</v>
       </c>
       <c r="R9" t="n">
-        <v>6944155</v>
+        <v>6944152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1730,10 +1716,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511080</v>
+        <v>124511018</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1742,25 +1728,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1773,14 +1759,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458100</v>
+        <v>458095</v>
       </c>
       <c r="R10" t="n">
-        <v>6944149</v>
+        <v>6944168</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1840,9 +1826,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1860,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124510904</v>
+        <v>124511273</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,21 +1867,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1903,14 +1894,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458110</v>
+        <v>458076</v>
       </c>
       <c r="R11" t="n">
-        <v>6944193</v>
+        <v>6944155</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1962,17 +1953,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1990,10 +1981,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124510922</v>
+        <v>124510904</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2006,21 +1997,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2120,10 +2111,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511528</v>
+        <v>124511723</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2136,21 +2127,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2163,14 +2154,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458148</v>
+        <v>458198</v>
       </c>
       <c r="R13" t="n">
-        <v>6944110</v>
+        <v>6944084</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2222,17 +2213,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2250,7 +2241,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511124</v>
+        <v>124511080</v>
       </c>
       <c r="B14" t="n">
         <v>91012</v>
@@ -2284,16 +2275,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458128</v>
+        <v>458100</v>
       </c>
       <c r="R14" t="n">
         <v>6944149</v>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511528</v>
+        <v>124511616</v>
       </c>
       <c r="B2" t="n">
         <v>91012</v>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458148</v>
+        <v>458165</v>
       </c>
       <c r="R2" t="n">
-        <v>6944110</v>
+        <v>6944152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,6 +760,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -777,17 +782,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511471</v>
+        <v>124511262</v>
       </c>
       <c r="B3" t="n">
-        <v>91592</v>
+        <v>91457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1179</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -848,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458133</v>
+        <v>458076</v>
       </c>
       <c r="R3" t="n">
-        <v>6944117</v>
+        <v>6944155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,17 +912,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511262</v>
+        <v>124511080</v>
       </c>
       <c r="B4" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +952,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -978,14 +983,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458076</v>
+        <v>458100</v>
       </c>
       <c r="R4" t="n">
-        <v>6944155</v>
+        <v>6944149</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1065,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124510922</v>
+        <v>124511124</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,41 +1086,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458110</v>
+        <v>458128</v>
       </c>
       <c r="R5" t="n">
-        <v>6944193</v>
+        <v>6944149</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1167,17 +1168,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511124</v>
+        <v>124511723</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,37 +1212,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458128</v>
+        <v>458198</v>
       </c>
       <c r="R6" t="n">
-        <v>6944149</v>
+        <v>6944084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1321,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511683</v>
+        <v>124511273</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,21 +1342,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1364,14 +1369,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458193</v>
+        <v>458076</v>
       </c>
       <c r="R7" t="n">
-        <v>6944142</v>
+        <v>6944155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1451,10 +1456,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124511616</v>
+        <v>124511576</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1538,7 +1543,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En låga med ullticka på</t>
+          <t>En låga med flertal kroppar på</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1558,17 +1563,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1586,7 +1591,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511633</v>
+        <v>124510904</v>
       </c>
       <c r="B9" t="n">
         <v>91299</v>
@@ -1629,14 +1634,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458165</v>
+        <v>458110</v>
       </c>
       <c r="R9" t="n">
-        <v>6944152</v>
+        <v>6944193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1688,17 +1693,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1716,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511018</v>
+        <v>124511528</v>
       </c>
       <c r="B10" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1728,25 +1733,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1759,14 +1764,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458095</v>
+        <v>458148</v>
       </c>
       <c r="R10" t="n">
-        <v>6944168</v>
+        <v>6944110</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1818,22 +1823,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511273</v>
+        <v>124511018</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1863,25 +1863,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1894,14 +1894,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458076</v>
+        <v>458095</v>
       </c>
       <c r="R11" t="n">
-        <v>6944155</v>
+        <v>6944168</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1961,9 +1961,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1981,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124510904</v>
+        <v>124510922</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1997,21 +2002,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2111,10 +2116,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511723</v>
+        <v>124511471</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91592</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2123,25 +2128,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1179</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2154,14 +2159,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458198</v>
+        <v>458133</v>
       </c>
       <c r="R13" t="n">
-        <v>6944084</v>
+        <v>6944117</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2213,17 +2218,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2241,10 +2246,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511080</v>
+        <v>124511683</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2257,21 +2262,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2284,14 +2289,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458100</v>
+        <v>458193</v>
       </c>
       <c r="R14" t="n">
-        <v>6944149</v>
+        <v>6944142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511262</v>
+        <v>124511528</v>
       </c>
       <c r="B3" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -853,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458076</v>
+        <v>458148</v>
       </c>
       <c r="R3" t="n">
-        <v>6944155</v>
+        <v>6944110</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,17 +912,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511080</v>
+        <v>124511262</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,25 +952,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -983,14 +983,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458100</v>
+        <v>458076</v>
       </c>
       <c r="R4" t="n">
-        <v>6944149</v>
+        <v>6944155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511124</v>
+        <v>124511018</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,41 +1082,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458128</v>
+        <v>458095</v>
       </c>
       <c r="R5" t="n">
-        <v>6944149</v>
+        <v>6944168</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1176,9 +1180,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1326,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511273</v>
+        <v>124510904</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,21 +1351,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1369,14 +1378,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458076</v>
+        <v>458110</v>
       </c>
       <c r="R7" t="n">
-        <v>6944155</v>
+        <v>6944193</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1428,17 +1437,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1591,10 +1600,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124510904</v>
+        <v>124511124</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1607,41 +1616,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458110</v>
+        <v>458128</v>
       </c>
       <c r="R9" t="n">
-        <v>6944193</v>
+        <v>6944149</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1693,17 +1698,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1721,10 +1726,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511528</v>
+        <v>124511471</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1733,25 +1738,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1764,14 +1769,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458148</v>
+        <v>458133</v>
       </c>
       <c r="R10" t="n">
-        <v>6944110</v>
+        <v>6944117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1851,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511018</v>
+        <v>124511080</v>
       </c>
       <c r="B11" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1863,25 +1868,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1894,14 +1899,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458095</v>
+        <v>458100</v>
       </c>
       <c r="R11" t="n">
-        <v>6944168</v>
+        <v>6944149</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1961,14 +1966,9 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124510922</v>
+        <v>124511273</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2002,21 +2002,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2029,14 +2029,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458110</v>
+        <v>458076</v>
       </c>
       <c r="R12" t="n">
-        <v>6944193</v>
+        <v>6944155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2088,17 +2088,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511471</v>
+        <v>124510922</v>
       </c>
       <c r="B13" t="n">
-        <v>91592</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2128,25 +2128,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1179</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2159,14 +2159,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458133</v>
+        <v>458110</v>
       </c>
       <c r="R13" t="n">
-        <v>6944117</v>
+        <v>6944193</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511616</v>
+        <v>124511727</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458165</v>
+        <v>458198</v>
       </c>
       <c r="R2" t="n">
-        <v>6944152</v>
+        <v>6944084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +758,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124511528</v>
+        <v>124510904</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -853,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458148</v>
+        <v>458110</v>
       </c>
       <c r="R3" t="n">
-        <v>6944110</v>
+        <v>6944193</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1070,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511018</v>
+        <v>124511683</v>
       </c>
       <c r="B5" t="n">
-        <v>91592</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,25 +1077,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1179</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1113,14 +1108,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458095</v>
+        <v>458193</v>
       </c>
       <c r="R5" t="n">
-        <v>6944168</v>
+        <v>6944142</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1180,14 +1175,9 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1205,7 +1195,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511723</v>
+        <v>124511576</v>
       </c>
       <c r="B6" t="n">
         <v>91299</v>
@@ -1248,14 +1238,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458198</v>
+        <v>458165</v>
       </c>
       <c r="R6" t="n">
-        <v>6944084</v>
+        <v>6944152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1290,6 +1280,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En låga med flertal kroppar på</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1307,17 +1302,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124510904</v>
+        <v>124511471</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>91592</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1179</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1378,14 +1373,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458110</v>
+        <v>458133</v>
       </c>
       <c r="R7" t="n">
-        <v>6944193</v>
+        <v>6944117</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1465,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124511576</v>
+        <v>124511616</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1481,21 +1476,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1552,7 +1547,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En låga med flertal kroppar på</t>
+          <t>En låga med ullticka på</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,17 +1567,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1600,10 +1595,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511124</v>
+        <v>124511018</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1612,41 +1607,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458128</v>
+        <v>458095</v>
       </c>
       <c r="R9" t="n">
-        <v>6944149</v>
+        <v>6944168</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1706,9 +1705,14 @@
           <t>Picea abies subsp. abies</t>
         </is>
       </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1726,10 +1730,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511471</v>
+        <v>124511528</v>
       </c>
       <c r="B10" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1738,25 +1742,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1769,14 +1773,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458133</v>
+        <v>458148</v>
       </c>
       <c r="R10" t="n">
-        <v>6944117</v>
+        <v>6944110</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1856,10 +1860,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124511080</v>
+        <v>124510922</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,21 +1876,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1899,14 +1903,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458100</v>
+        <v>458110</v>
       </c>
       <c r="R11" t="n">
-        <v>6944149</v>
+        <v>6944193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1958,17 +1962,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1986,7 +1990,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124511273</v>
+        <v>124511080</v>
       </c>
       <c r="B12" t="n">
         <v>91012</v>
@@ -2029,14 +2033,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458076</v>
+        <v>458100</v>
       </c>
       <c r="R12" t="n">
-        <v>6944155</v>
+        <v>6944149</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2116,10 +2120,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124510922</v>
+        <v>124511273</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2132,21 +2136,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2159,14 +2163,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458110</v>
+        <v>458076</v>
       </c>
       <c r="R13" t="n">
-        <v>6944193</v>
+        <v>6944155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2218,17 +2222,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2246,10 +2250,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511683</v>
+        <v>124511124</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2262,41 +2266,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458193</v>
+        <v>458128</v>
       </c>
       <c r="R14" t="n">
-        <v>6944142</v>
+        <v>6944149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124511727</v>
+        <v>124510904</v>
       </c>
       <c r="B2" t="n">
         <v>91299</v>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6944084, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458198</v>
+        <v>458110</v>
       </c>
       <c r="R2" t="n">
-        <v>6944084</v>
+        <v>6944193</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,17 +777,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124510904</v>
+        <v>124511018</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>91592</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944168, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458110</v>
+        <v>458095</v>
       </c>
       <c r="R3" t="n">
-        <v>6944193</v>
+        <v>6944168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,17 +907,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Gammal låga</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies # Gammal låga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124511262</v>
+        <v>124511616</v>
       </c>
       <c r="B4" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +952,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -978,14 +983,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458076</v>
+        <v>458165</v>
       </c>
       <c r="R4" t="n">
-        <v>6944155</v>
+        <v>6944152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,6 +1023,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En låga med ullticka på</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,7 +1075,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124511683</v>
+        <v>124511727</v>
       </c>
       <c r="B5" t="n">
         <v>91299</v>
@@ -1108,14 +1118,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6944142, Jmt</t>
+          <t>6944084, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458193</v>
+        <v>458198</v>
       </c>
       <c r="R5" t="n">
-        <v>6944142</v>
+        <v>6944084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1195,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124511576</v>
+        <v>124511262</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,25 +1217,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1238,14 +1248,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458165</v>
+        <v>458076</v>
       </c>
       <c r="R6" t="n">
-        <v>6944152</v>
+        <v>6944155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,11 +1290,6 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En låga med flertal kroppar på</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1302,17 +1307,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1330,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124511471</v>
+        <v>124511528</v>
       </c>
       <c r="B7" t="n">
-        <v>91592</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1347,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1373,14 +1378,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6944117, Jmt</t>
+          <t>6944110, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458133</v>
+        <v>458148</v>
       </c>
       <c r="R7" t="n">
-        <v>6944117</v>
+        <v>6944110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1460,7 +1465,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124511616</v>
+        <v>124511124</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1494,23 +1499,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>458128, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458165</v>
+        <v>458128</v>
       </c>
       <c r="R8" t="n">
-        <v>6944152</v>
+        <v>6944149</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,11 +1544,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En låga med ullticka på</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1595,10 +1591,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511018</v>
+        <v>124511576</v>
       </c>
       <c r="B9" t="n">
-        <v>91592</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1607,25 +1603,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1179</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1638,14 +1634,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944168, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458095</v>
+        <v>458165</v>
       </c>
       <c r="R9" t="n">
-        <v>6944168</v>
+        <v>6944152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1680,6 +1676,11 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En låga med flertal kroppar på</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1697,22 +1698,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Gammal låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Gammal låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1730,10 +1726,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124511528</v>
+        <v>124510922</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,21 +1742,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1773,14 +1769,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6944110, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458148</v>
+        <v>458110</v>
       </c>
       <c r="R10" t="n">
-        <v>6944110</v>
+        <v>6944193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1860,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124510922</v>
+        <v>124511683</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1876,21 +1872,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1903,14 +1899,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944142, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458110</v>
+        <v>458193</v>
       </c>
       <c r="R11" t="n">
-        <v>6944193</v>
+        <v>6944142</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1962,17 +1958,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1990,7 +1986,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124511080</v>
+        <v>124511273</v>
       </c>
       <c r="B12" t="n">
         <v>91012</v>
@@ -2033,14 +2029,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6944149, Jmt</t>
+          <t>6944155, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458100</v>
+        <v>458076</v>
       </c>
       <c r="R12" t="n">
-        <v>6944149</v>
+        <v>6944155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2120,7 +2116,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124511273</v>
+        <v>124511080</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -2163,14 +2159,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6944155, Jmt</t>
+          <t>6944149, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458076</v>
+        <v>458100</v>
       </c>
       <c r="R13" t="n">
-        <v>6944155</v>
+        <v>6944149</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2250,10 +2246,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124511124</v>
+        <v>124511471</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91592</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2262,41 +2258,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>458128, Jmt</t>
+          <t>6944117, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458128</v>
+        <v>458133</v>
       </c>
       <c r="R14" t="n">
-        <v>6944149</v>
+        <v>6944117</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2348,17 +2348,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 16051-2025 artfynd.xlsx
+++ b/artfynd/A 16051-2025 artfynd.xlsx
@@ -1591,10 +1591,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124511576</v>
+        <v>124510922</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1634,14 +1634,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6944152, Jmt</t>
+          <t>06944193, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458165</v>
+        <v>458110</v>
       </c>
       <c r="R9" t="n">
-        <v>6944152</v>
+        <v>6944193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,11 +1674,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En låga med flertal kroppar på</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1726,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124510922</v>
+        <v>124511576</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1742,21 +1737,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1769,14 +1764,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>06944193, Jmt</t>
+          <t>6944152, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458110</v>
+        <v>458165</v>
       </c>
       <c r="R10" t="n">
-        <v>6944193</v>
+        <v>6944152</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,6 +1804,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>En låga med flertal kroppar på</t>
         </is>
       </c>
       <c r="AD10" t="b">
